--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rithesh\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{245A7152-55DB-4436-A78C-C3F5AEDD55AE}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="12980" windowHeight="16090" activeTab="1" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -139,13 +139,16 @@
   </si>
   <si>
     <t xml:space="preserve">cia 1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">event </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,6 +195,12 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -3060,7 +3069,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CECD43-374A-4C54-B61A-429B503DADAE}">
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -3114,7 +3123,31 @@
         <v>33</v>
       </c>
     </row>
+    <row r="3" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>46262</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="G3" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{245A7152-55DB-4436-A78C-C3F5AEDD55AE}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A01F63-96E6-41B1-907E-C5CF50C9B840}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="35">
   <si>
     <t>Date</t>
   </si>
@@ -330,6 +330,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -3136,12 +3140,8 @@
       <c r="D3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>20</v>
-      </c>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
       <c r="G3" t="s">
         <v>34</v>
       </c>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{31A01F63-96E6-41B1-907E-C5CF50C9B840}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB9E5A78-8649-49F3-88F4-31F01433A939}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -142,6 +142,9 @@
   </si>
   <si>
     <t xml:space="preserve">event </t>
+  </si>
+  <si>
+    <t>SIP (DRAFT)</t>
   </si>
 </sst>
 </file>
@@ -3073,7 +3076,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CECD43-374A-4C54-B61A-429B503DADAE}">
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -3146,6 +3149,25 @@
         <v>34</v>
       </c>
     </row>
+    <row r="4" spans="1:8" ht="16" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>46265</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB9E5A78-8649-49F3-88F4-31F01433A939}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D020FF1-A213-4D82-8D2B-531A81E29EA1}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="37">
   <si>
     <t>Date</t>
   </si>
@@ -145,6 +145,9 @@
   </si>
   <si>
     <t>SIP (DRAFT)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fun game </t>
   </si>
 </sst>
 </file>
@@ -274,7 +277,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -318,6 +321,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3076,7 +3080,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CECD43-374A-4C54-B61A-429B503DADAE}">
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.7265625" bestFit="1" customWidth="1"/>
@@ -3168,6 +3172,17 @@
         <v>35</v>
       </c>
     </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" s="15">
+        <v>46266</v>
+      </c>
+      <c r="B5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>36</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5D020FF1-A213-4D82-8D2B-531A81E29EA1}"/>
+  <xr:revisionPtr revIDLastSave="13" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B929B13D-BA9C-454F-99A7-FC9D31AEA001}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" activeTab="1" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
   <sheets>
     <sheet name="time table" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="560" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -145,9 +145,6 @@
   </si>
   <si>
     <t>SIP (DRAFT)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fun game </t>
   </si>
 </sst>
 </file>
@@ -3173,15 +3170,7 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="15">
-        <v>46266</v>
-      </c>
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
+      <c r="A5" s="15"/>
     </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="13" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B929B13D-BA9C-454F-99A7-FC9D31AEA001}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61570DDA-D4EE-4111-884E-C3099FA8D4F7}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="558" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="534" uniqueCount="36">
   <si>
     <t>Date</t>
   </si>
@@ -1774,114 +1774,6 @@
       </c>
       <c r="I41" s="10"/>
     </row>
-    <row r="42" spans="1:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="A42" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D42" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F42" s="7" t="s">
-        <v>19</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H42" s="7">
-        <v>301</v>
-      </c>
-      <c r="I42" s="8"/>
-    </row>
-    <row r="43" spans="1:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="A43" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F43" s="9" t="s">
-        <v>22</v>
-      </c>
-      <c r="G43" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="H43" s="9">
-        <v>301</v>
-      </c>
-      <c r="I43" s="10"/>
-    </row>
-    <row r="44" spans="1:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="A44" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D44" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="F44" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="H44" s="7">
-        <v>301</v>
-      </c>
-      <c r="I44" s="8"/>
-    </row>
-    <row r="45" spans="1:9" ht="16" x14ac:dyDescent="0.35">
-      <c r="A45" s="3">
-        <v>46266</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D45" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>21</v>
-      </c>
-      <c r="F45" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="G45" s="9" t="s">
-        <v>20</v>
-      </c>
-      <c r="H45" s="9">
-        <v>301</v>
-      </c>
-      <c r="I45" s="10"/>
-    </row>
     <row r="46" spans="1:9" ht="16" x14ac:dyDescent="0.35">
       <c r="A46" s="3">
         <v>46267</v>

--- a/class-data.xlsx
+++ b/class-data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/d7ab4f87bcbcc61e/Documents/GitHub/time table/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{61570DDA-D4EE-4111-884E-C3099FA8D4F7}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="8_{19B0D046-57F0-406B-95B0-D5FC8226E0B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EF8E2CD0-48F4-4095-A2C2-7DB5DCED4410}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="16220" xr2:uid="{1A9FD5BF-2FEB-4584-A08A-12E61D1B464F}"/>
   </bookViews>
@@ -1905,7 +1905,7 @@
         <v>30</v>
       </c>
       <c r="H50" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I50" s="8"/>
     </row>
@@ -1931,8 +1931,8 @@
       <c r="G51" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H51" s="9">
-        <v>301</v>
+      <c r="H51" s="7">
+        <v>308</v>
       </c>
       <c r="I51" s="10"/>
     </row>
@@ -1959,7 +1959,7 @@
         <v>30</v>
       </c>
       <c r="H52" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I52" s="8"/>
     </row>
@@ -1985,8 +1985,8 @@
       <c r="G53" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H53" s="9">
-        <v>301</v>
+      <c r="H53" s="7">
+        <v>308</v>
       </c>
       <c r="I53" s="10"/>
     </row>
@@ -2013,7 +2013,7 @@
         <v>30</v>
       </c>
       <c r="H54" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I54" s="8"/>
     </row>
@@ -2039,8 +2039,8 @@
       <c r="G55" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H55" s="9">
-        <v>301</v>
+      <c r="H55" s="7">
+        <v>308</v>
       </c>
       <c r="I55" s="10"/>
     </row>
@@ -2067,7 +2067,7 @@
         <v>30</v>
       </c>
       <c r="H56" s="7">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="I56" s="8"/>
     </row>
@@ -2093,8 +2093,8 @@
       <c r="G57" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="H57" s="9">
-        <v>301</v>
+      <c r="H57" s="7">
+        <v>308</v>
       </c>
       <c r="I57" s="10"/>
     </row>
